--- a/classificacao.xlsx
+++ b/classificacao.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E3" t="b">
@@ -791,7 +791,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E10" t="b">
@@ -865,7 +865,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E12" t="b">
@@ -976,7 +976,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E15" t="b">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E28" t="b">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E31" t="b">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E38" t="b">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E40" t="b">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E41" t="b">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E49" t="b">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E50" t="b">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E55" t="b">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E56" t="b">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E63" t="b">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E69" t="b">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E70" t="b">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E71" t="b">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E72" t="b">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E73" t="b">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E74" t="b">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E78" t="b">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E85" t="b">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E90" t="b">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E92" t="b">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E96" t="b">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E105" t="b">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E107" t="b">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -4676,7 +4676,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -4787,7 +4787,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E121" t="b">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E123" t="b">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E130" t="b">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E137" t="b">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E144" t="b">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E155" t="b">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -6600,7 +6600,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -6748,7 +6748,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E171" t="b">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E193" t="b">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E196" t="b">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E200" t="b">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E209" t="b">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E212" t="b">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E213" t="b">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E215" t="b">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E216" t="b">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E221" t="b">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E222" t="b">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E226" t="b">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E227" t="b">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E228" t="b">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E229" t="b">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E230" t="b">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E233" t="b">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E234" t="b">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E237" t="b">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E240" t="b">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E241" t="b">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E242" t="b">
@@ -9412,7 +9412,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E243" t="b">
@@ -9560,7 +9560,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E247" t="b">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E248" t="b">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E249" t="b">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E250" t="b">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E251" t="b">
@@ -9745,7 +9745,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E252" t="b">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E253" t="b">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E256" t="b">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E257" t="b">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E264" t="b">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E265" t="b">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E267" t="b">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E269" t="b">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MONOREPO_MAVEN</t>
         </is>
       </c>
       <c r="E277" t="b">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E278" t="b">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E281" t="b">
@@ -10892,7 +10892,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E283" t="b">
@@ -11077,7 +11077,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E288" t="b">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E289" t="b">
@@ -11151,7 +11151,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E290" t="b">
@@ -11225,7 +11225,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E292" t="b">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E294" t="b">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E298" t="b">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E302" t="b">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E303" t="b">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E305" t="b">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E306" t="b">
@@ -11780,7 +11780,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E307" t="b">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E308" t="b">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E310" t="b">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E315" t="b">
@@ -12298,7 +12298,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E321" t="b">
@@ -12409,7 +12409,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E324" t="b">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E326" t="b">
@@ -12557,7 +12557,7 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E328" t="b">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E331" t="b">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E333" t="b">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E335" t="b">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E336" t="b">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E341" t="b">
@@ -13075,7 +13075,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E342" t="b">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E343" t="b">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E344" t="b">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E346" t="b">
@@ -13260,7 +13260,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E347" t="b">
@@ -13556,7 +13556,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E355" t="b">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E360" t="b">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E363" t="b">
@@ -13904,27 +13904,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>171</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MULTIPROJETOS</t>
+          <t>SINGLE_REPO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">

--- a/classificacao.xlsx
+++ b/classificacao.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E2" t="b">
@@ -569,7 +569,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -606,7 +606,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -717,7 +717,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E8" t="b">
@@ -754,7 +754,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E9" t="b">
@@ -828,7 +828,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E11" t="b">
@@ -902,7 +902,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E13" t="b">
@@ -939,7 +939,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E14" t="b">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E16" t="b">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E17" t="b">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E18" t="b">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E21" t="b">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E23" t="b">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E26" t="b">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E27" t="b">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E29" t="b">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E30" t="b">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E32" t="b">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E33" t="b">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E34" t="b">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E35" t="b">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E36" t="b">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E39" t="b">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E42" t="b">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E43" t="b">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E60" t="b">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E61" t="b">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E62" t="b">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E66" t="b">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E91" t="b">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E93" t="b">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E95" t="b">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E103" t="b">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E104" t="b">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E106" t="b">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E111" t="b">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E129" t="b">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E132" t="b">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E135" t="b">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E136" t="b">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E140" t="b">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E141" t="b">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E142" t="b">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E145" t="b">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E147" t="b">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E150" t="b">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E151" t="b">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E154" t="b">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E156" t="b">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E160" t="b">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E162" t="b">
@@ -6452,7 +6452,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E163" t="b">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -6674,7 +6674,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E169" t="b">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -6785,7 +6785,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E172" t="b">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E174" t="b">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E178" t="b">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -7303,7 +7303,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E186" t="b">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E187" t="b">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E188" t="b">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E192" t="b">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E195" t="b">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E198" t="b">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E203" t="b">
@@ -7969,7 +7969,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E204" t="b">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E205" t="b">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E206" t="b">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E207" t="b">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E208" t="b">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E210" t="b">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E211" t="b">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E214" t="b">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E218" t="b">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E219" t="b">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E223" t="b">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E224" t="b">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E225" t="b">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E231" t="b">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E232" t="b">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E235" t="b">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E236" t="b">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E245" t="b">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E246" t="b">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E254" t="b">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E255" t="b">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E258" t="b">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E259" t="b">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E271" t="b">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E272" t="b">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E274" t="b">
@@ -10596,7 +10596,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E275" t="b">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E277" t="b">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E279" t="b">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E280" t="b">
@@ -10855,7 +10855,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E282" t="b">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E284" t="b">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E285" t="b">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E293" t="b">
@@ -11336,7 +11336,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E295" t="b">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E300" t="b">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E301" t="b">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E304" t="b">
@@ -11965,7 +11965,7 @@
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E312" t="b">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E316" t="b">
@@ -12150,7 +12150,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E317" t="b">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E318" t="b">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E319" t="b">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E320" t="b">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E323" t="b">
@@ -12520,7 +12520,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E327" t="b">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E329" t="b">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E330" t="b">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E337" t="b">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E338" t="b">
@@ -13001,7 +13001,7 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E340" t="b">
@@ -13186,7 +13186,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E345" t="b">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E349" t="b">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E350" t="b">
@@ -13408,7 +13408,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E351" t="b">
@@ -13482,7 +13482,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E353" t="b">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E354" t="b">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E356" t="b">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E357" t="b">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E358" t="b">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E362" t="b">
@@ -13882,7 +13882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13900,40 +13900,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>153</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MULTIPROJETOS</t>
+          <t>SINGLE_REPO</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>144</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SINGLE_REPO</t>
+          <t>DESCONHECIDO</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>DESCONHECIDO</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
         <v>21</v>
       </c>
     </row>

--- a/classificacao.xlsx
+++ b/classificacao.xlsx
@@ -6637,7 +6637,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>MULTIPROJETOS</t>
+          <t>MONOREPO_MAVEN</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>MULTIPROJETOS</t>
+          <t>MONOREPO_MAVEN</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>MULTIPROJETOS</t>
+          <t>MONOREPO_MAVEN</t>
         </is>
       </c>
       <c r="E255" t="b">
@@ -13882,7 +13882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13904,7 +13904,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="3">
@@ -13925,6 +13925,16 @@
       </c>
       <c r="B4" t="n">
         <v>21</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MONOREPO_MAVEN</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/classificacao.xlsx
+++ b/classificacao.xlsx
@@ -6637,7 +6637,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>MULTIPROJETOS</t>
+          <t>SINGLE_REPO</t>
         </is>
       </c>
       <c r="E253" t="b">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>MONOREPO_MAVEN</t>
+          <t>MULTIPROJETOS</t>
         </is>
       </c>
       <c r="E255" t="b">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>MULTIPROJETOS</t>
+          <t>SINGLE_REPO</t>
         </is>
       </c>
       <c r="E256" t="b">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>MULTIPROJETOS</t>
+          <t>SINGLE_REPO</t>
         </is>
       </c>
       <c r="E346" t="b">
@@ -13882,7 +13882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13914,7 +13914,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -13925,16 +13925,6 @@
       </c>
       <c r="B4" t="n">
         <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MONOREPO_MAVEN</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/classificacao.xlsx
+++ b/classificacao.xlsx
@@ -2620,7 +2620,7 @@
         <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60">
@@ -13958,7 +13958,7 @@
         <v>13756</v>
       </c>
       <c r="B2" t="n">
-        <v>312493</v>
+        <v>312494</v>
       </c>
     </row>
   </sheetData>
